--- a/docs/Lifelikegame_Phase_Progress_Tracker_CN.xlsx
+++ b/docs/Lifelikegame_Phase_Progress_Tracker_CN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\folder\projects\lifelikegame\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFB3B743-F9C1-4688-86DB-0FC3C70FC993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB7FBD6E-734C-49F2-A87C-82CA5272B855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="_Lists" sheetId="1" r:id="rId1"/>
@@ -1904,9 +1904,6 @@
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1918,6 +1915,9 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3232,22 +3232,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="19.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>517</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
     </row>
     <row r="2" spans="1:14" ht="14.4">
       <c r="A2" s="6" t="s">
@@ -3268,90 +3268,90 @@
       <c r="N2" s="6"/>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="L4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="M4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="N4" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="27.6">
-      <c r="A5" s="4">
+      <c r="A5" s="3">
         <v>77</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>521</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="4">
         <v>0</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="3" t="s">
         <v>522</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="3" t="s">
         <v>523</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="L5" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="M5" s="4" t="s">
+      <c r="M5" s="3" t="s">
         <v>525</v>
       </c>
-      <c r="N5" s="4" t="s">
+      <c r="N5" s="3" t="s">
         <v>526</v>
       </c>
     </row>
@@ -3483,14 +3483,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="19.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>527</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
     </row>
     <row r="2" spans="1:6" ht="14.4">
       <c r="A2" s="6" t="s">
@@ -3503,222 +3503,222 @@
       <c r="F2" s="6"/>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>531</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="3">
+      <c r="A5" s="2">
         <v>1</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>533</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="27.6">
-      <c r="A6" s="3">
+      <c r="A6" s="2">
         <v>2</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="2" t="s">
         <v>536</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="27.6">
-      <c r="A7" s="3">
+      <c r="A7" s="2">
         <v>3</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="2" t="s">
         <v>538</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="27.6">
-      <c r="A8" s="3">
+      <c r="A8" s="2">
         <v>4</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="2" t="s">
         <v>541</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="27.6">
-      <c r="A9" s="3">
+      <c r="A9" s="2">
         <v>5</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="2" t="s">
         <v>543</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3">
+      <c r="A10" s="2">
         <v>6</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="2" t="s">
         <v>546</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3">
+      <c r="A11" s="2">
         <v>7</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="2" t="s">
         <v>548</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="27.6">
-      <c r="A12" s="3">
+      <c r="A12" s="2">
         <v>8</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="2" t="s">
         <v>551</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3">
+      <c r="A13" s="2">
         <v>9</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="2" t="s">
         <v>553</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="27.6">
-      <c r="A14" s="3">
+      <c r="A14" s="2">
         <v>10</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="2" t="s">
         <v>556</v>
       </c>
     </row>
@@ -3768,234 +3768,234 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="19.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>557</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>560</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>562</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>563</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="41.4">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>571</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>573</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>574</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="2" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="27.6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="2" t="s">
         <v>576</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>578</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="2" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="2" t="s">
         <v>579</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>580</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="2" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="27.6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="2" t="s">
         <v>583</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="2" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="2" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="27.6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="2" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="2" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="2" t="s">
         <v>592</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="2" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>594</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="2" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="27.6">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="2" t="s">
         <v>597</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="2" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="27.6">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="2" t="s">
         <v>571</v>
       </c>
     </row>
@@ -4032,22 +4032,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="19.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
     </row>
     <row r="2" spans="1:14" ht="14.4">
       <c r="A2" s="6" t="s">
@@ -4068,390 +4068,390 @@
       <c r="N2" s="6"/>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="L4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="M4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="N4" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="27.6">
-      <c r="A5" s="4">
+      <c r="A5" s="3">
         <v>1</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="4">
         <v>100</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="L5" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="M5" s="4" t="s">
+      <c r="M5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="N5" s="4"/>
+      <c r="N5" s="3"/>
     </row>
     <row r="6" spans="1:14" ht="41.4">
-      <c r="A6" s="4">
+      <c r="A6" s="3">
         <v>2</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="4">
         <v>100</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="L6" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="M6" s="4" t="s">
+      <c r="M6" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="N6" s="4" t="s">
+      <c r="N6" s="3" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="27.6">
-      <c r="A7" s="4">
+      <c r="A7" s="3">
         <v>3</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="4">
         <v>100</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="J7" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="K7" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="L7" s="4" t="s">
+      <c r="L7" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="M7" s="4" t="s">
+      <c r="M7" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="N7" s="4"/>
+      <c r="N7" s="3"/>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" s="4">
+      <c r="A8" s="3">
         <v>4</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="4">
         <v>100</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="J8" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="L8" s="4" t="s">
+      <c r="L8" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="M8" s="4" t="s">
+      <c r="M8" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="N8" s="4"/>
+      <c r="N8" s="3"/>
     </row>
     <row r="9" spans="1:14" ht="27.6">
-      <c r="A9" s="4">
+      <c r="A9" s="3">
         <v>5</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="4">
         <v>100</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="J9" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="K9" s="4" t="s">
+      <c r="K9" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="4" t="s">
+      <c r="L9" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="M9" s="4" t="s">
+      <c r="M9" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="N9" s="4"/>
+      <c r="N9" s="3"/>
     </row>
     <row r="10" spans="1:14" ht="41.4">
-      <c r="A10" s="4">
+      <c r="A10" s="3">
         <v>7</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="4">
         <v>100</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="J10" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="K10" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="L10" s="4" t="s">
+      <c r="L10" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M10" s="4" t="s">
+      <c r="M10" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="N10" s="4" t="s">
+      <c r="N10" s="3" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="27.6">
-      <c r="A11" s="4">
+      <c r="A11" s="3">
         <v>8</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11" s="4">
         <v>100</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="J11" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="K11" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="L11" s="4" t="s">
+      <c r="L11" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="M11" s="4" t="s">
+      <c r="M11" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="N11" s="4" t="s">
+      <c r="N11" s="3" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="41.4">
-      <c r="A12" s="4">
+      <c r="A12" s="3">
         <v>9</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="4">
         <v>100</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J12" s="4" t="s">
+      <c r="J12" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="K12" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="L12" s="4" t="s">
+      <c r="L12" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="M12" s="4" t="s">
+      <c r="M12" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="N12" s="4"/>
+      <c r="N12" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4589,22 +4589,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="19.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
     </row>
     <row r="2" spans="1:14" ht="14.4">
       <c r="A2" s="6" t="s">
@@ -4625,702 +4625,702 @@
       <c r="N2" s="6"/>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="L4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="M4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="N4" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="27.6">
-      <c r="A5" s="4">
+      <c r="A5" s="3">
         <v>10</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="4">
+        <v>100</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="N5" s="3"/>
+    </row>
+    <row r="6" spans="1:14" ht="27.6">
+      <c r="A6" s="3">
+        <v>11</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H6" s="4">
         <v>0</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="41.4">
+      <c r="A7" s="3">
         <v>12</v>
       </c>
-      <c r="J5" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="N5" s="4"/>
-    </row>
-    <row r="6" spans="1:14" ht="27.6">
-      <c r="A6" s="4">
+      <c r="B7" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="G7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="27.6">
+      <c r="A8" s="3">
+        <v>13</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C8" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="27.6">
+      <c r="A9" s="3">
+        <v>14</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="27.6">
+      <c r="A10" s="3">
+        <v>15</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="27.6">
+      <c r="A11" s="3">
+        <v>16</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="27.6">
+      <c r="A12" s="3">
+        <v>19</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" ht="27.6">
+      <c r="A13" s="3">
+        <v>20</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="27.6">
+      <c r="A14" s="3">
+        <v>21</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E6" s="4" t="s">
+      <c r="D14" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="27.6">
+      <c r="A15" s="3">
+        <v>31</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G6" s="4" t="s">
+      <c r="F15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H15" s="4">
         <v>0</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="27.6">
+      <c r="A16" s="3">
+        <v>32</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="27.6">
+      <c r="A17" s="3">
+        <v>33</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J6" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="M6" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N6" s="4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="41.4">
-      <c r="A7" s="4">
+      <c r="J17" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="27.6">
+      <c r="A18" s="3">
+        <v>34</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H18" s="4">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="J18" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="27.6">
+      <c r="A19" s="3">
+        <v>35</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="E7" s="4" t="s">
+      <c r="C19" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F19" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G19" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H19" s="4">
         <v>0</v>
       </c>
-      <c r="I7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="N7" s="4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="27.6">
-      <c r="A8" s="4">
-        <v>13</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="H8" s="5">
-        <v>0</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="N8" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="27.6">
-      <c r="A9" s="4">
-        <v>14</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="H9" s="5">
-        <v>0</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="M9" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="N9" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="27.6">
-      <c r="A10" s="4">
-        <v>15</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="5">
-        <v>0</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="L10" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="M10" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="N10" s="4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="27.6">
-      <c r="A11" s="4">
-        <v>16</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="H11" s="5">
-        <v>0</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="L11" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="M11" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="N11" s="4" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="27.6">
-      <c r="A12" s="4">
-        <v>19</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="H12" s="5">
-        <v>0</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="L12" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="M12" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="N12" s="4"/>
-    </row>
-    <row r="13" spans="1:14" ht="27.6">
-      <c r="A13" s="4">
-        <v>20</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="H13" s="5">
-        <v>0</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="L13" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="N13" s="4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="27.6">
-      <c r="A14" s="4">
-        <v>21</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="H14" s="5">
-        <v>0</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="L14" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="M14" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N14" s="4" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="27.6">
-      <c r="A15" s="4">
-        <v>31</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="H15" s="5">
-        <v>0</v>
-      </c>
-      <c r="I15" s="4" t="s">
+      <c r="I19" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J15" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="L15" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="M15" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="N15" s="4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="27.6">
-      <c r="A16" s="4">
-        <v>32</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="H16" s="5">
-        <v>0</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="L16" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="M16" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="N16" s="4" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="27.6">
-      <c r="A17" s="4">
-        <v>33</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="H17" s="5">
-        <v>0</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="L17" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="M17" s="4" t="s">
+      <c r="J19" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="M19" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="N17" s="4" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="27.6">
-      <c r="A18" s="4">
-        <v>34</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="H18" s="5">
-        <v>0</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="L18" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="M18" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="N18" s="4" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="27.6">
-      <c r="A19" s="4">
-        <v>35</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="H19" s="5">
-        <v>0</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="K19" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="L19" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="M19" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="N19" s="4" t="s">
+      <c r="N19" s="3" t="s">
         <v>169</v>
       </c>
     </row>
@@ -5460,22 +5460,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="19.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
     </row>
     <row r="2" spans="1:14" ht="14.4">
       <c r="A2" s="6" t="s">
@@ -5496,614 +5496,614 @@
       <c r="N2" s="6"/>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="L4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="M4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="N4" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="27.6">
-      <c r="A5" s="4">
+      <c r="A5" s="3">
         <v>22</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="4">
         <v>0</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="L5" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="M5" s="4" t="s">
+      <c r="M5" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="N5" s="4" t="s">
+      <c r="N5" s="3" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="27.6">
-      <c r="A6" s="4">
+      <c r="A6" s="3">
         <v>23</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="4">
         <v>0</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="L6" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="M6" s="4" t="s">
+      <c r="M6" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="N6" s="4" t="s">
+      <c r="N6" s="3" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="27.6">
-      <c r="A7" s="4">
+      <c r="A7" s="3">
         <v>24</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="4">
         <v>0</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="J7" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="K7" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="L7" s="4" t="s">
+      <c r="L7" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="M7" s="4" t="s">
+      <c r="M7" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="N7" s="4" t="s">
+      <c r="N7" s="3" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="27.6">
-      <c r="A8" s="4">
+      <c r="A8" s="3">
         <v>27</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="4">
         <v>0</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="J8" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="L8" s="4" t="s">
+      <c r="L8" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="M8" s="4" t="s">
+      <c r="M8" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="N8" s="4"/>
+      <c r="N8" s="3"/>
     </row>
     <row r="9" spans="1:14" ht="27.6">
-      <c r="A9" s="4">
+      <c r="A9" s="3">
         <v>36</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="4">
         <v>0</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="J9" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="K9" s="4" t="s">
+      <c r="K9" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="L9" s="4" t="s">
+      <c r="L9" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="M9" s="4" t="s">
+      <c r="M9" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="N9" s="4" t="s">
+      <c r="N9" s="3" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="27.6">
-      <c r="A10" s="4">
+      <c r="A10" s="3">
         <v>38</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="4">
         <v>0</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="J10" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="K10" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="L10" s="4" t="s">
+      <c r="L10" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="M10" s="4" t="s">
+      <c r="M10" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="N10" s="4" t="s">
+      <c r="N10" s="3" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="27.6">
-      <c r="A11" s="4">
+      <c r="A11" s="3">
         <v>40</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11" s="4">
         <v>0</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="J11" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="K11" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="L11" s="4" t="s">
+      <c r="L11" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="M11" s="4" t="s">
+      <c r="M11" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="N11" s="4" t="s">
+      <c r="N11" s="3" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="27.6">
-      <c r="A12" s="4">
+      <c r="A12" s="3">
         <v>58</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="4">
         <v>0</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J12" s="4" t="s">
+      <c r="J12" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="K12" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="L12" s="4" t="s">
+      <c r="L12" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="M12" s="4" t="s">
+      <c r="M12" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="N12" s="4" t="s">
+      <c r="N12" s="3" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="27.6">
-      <c r="A13" s="4">
+      <c r="A13" s="3">
         <v>59</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H13" s="4">
         <v>0</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J13" s="4" t="s">
+      <c r="J13" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="K13" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="L13" s="4" t="s">
+      <c r="L13" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="M13" s="4" t="s">
+      <c r="M13" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="N13" s="4" t="s">
+      <c r="N13" s="3" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="27.6">
-      <c r="A14" s="4">
+      <c r="A14" s="3">
         <v>61</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H14" s="5">
+      <c r="H14" s="4">
         <v>0</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J14" s="4" t="s">
+      <c r="J14" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="K14" s="4" t="s">
+      <c r="K14" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="L14" s="4" t="s">
+      <c r="L14" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="M14" s="4" t="s">
+      <c r="M14" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="N14" s="4"/>
+      <c r="N14" s="3"/>
     </row>
     <row r="15" spans="1:14" ht="41.4">
-      <c r="A15" s="4">
+      <c r="A15" s="3">
         <v>66</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H15" s="4">
         <v>0</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="I15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J15" s="4" t="s">
+      <c r="J15" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="K15" s="4" t="s">
+      <c r="K15" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="L15" s="4" t="s">
+      <c r="L15" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="M15" s="4" t="s">
+      <c r="M15" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="N15" s="4" t="s">
+      <c r="N15" s="3" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="41.4">
-      <c r="A16" s="4">
+      <c r="A16" s="3">
         <v>67</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H16" s="5">
+      <c r="H16" s="4">
         <v>0</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="I16" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J16" s="4" t="s">
+      <c r="J16" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="K16" s="4" t="s">
+      <c r="K16" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="L16" s="4" t="s">
+      <c r="L16" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="M16" s="4" t="s">
+      <c r="M16" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="N16" s="4" t="s">
+      <c r="N16" s="3" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="27.6">
-      <c r="A17" s="4">
+      <c r="A17" s="3">
         <v>69</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H17" s="5">
+      <c r="H17" s="4">
         <v>0</v>
       </c>
-      <c r="I17" s="4" t="s">
+      <c r="I17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J17" s="4" t="s">
+      <c r="J17" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="K17" s="4" t="s">
+      <c r="K17" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="L17" s="4" t="s">
+      <c r="L17" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="M17" s="4" t="s">
+      <c r="M17" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="N17" s="4" t="s">
+      <c r="N17" s="3" t="s">
         <v>253</v>
       </c>
     </row>
@@ -6243,22 +6243,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="19.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
     </row>
     <row r="2" spans="1:14" ht="14.4">
       <c r="A2" s="6" t="s">
@@ -6279,354 +6279,354 @@
       <c r="N2" s="6"/>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="L4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="M4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="N4" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="27.6">
-      <c r="A5" s="4">
+      <c r="A5" s="3">
         <v>25</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="4">
         <v>0</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="L5" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="M5" s="4" t="s">
+      <c r="M5" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="N5" s="4" t="s">
+      <c r="N5" s="3" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="27.6">
-      <c r="A6" s="4">
+      <c r="A6" s="3">
         <v>26</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="4">
         <v>0</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="L6" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="M6" s="4" t="s">
+      <c r="M6" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="N6" s="4" t="s">
+      <c r="N6" s="3" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="41.4">
-      <c r="A7" s="4">
+      <c r="A7" s="3">
         <v>28</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="4">
         <v>0</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="J7" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="K7" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="L7" s="4" t="s">
+      <c r="L7" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="M7" s="4" t="s">
+      <c r="M7" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="N7" s="4" t="s">
+      <c r="N7" s="3" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="27.6">
-      <c r="A8" s="4">
+      <c r="A8" s="3">
         <v>37</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="4">
         <v>0</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="J8" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="L8" s="4" t="s">
+      <c r="L8" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="M8" s="4" t="s">
+      <c r="M8" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="N8" s="4" t="s">
+      <c r="N8" s="3" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="27.6">
-      <c r="A9" s="4">
+      <c r="A9" s="3">
         <v>65</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="4">
         <v>0</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="J9" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="K9" s="4" t="s">
+      <c r="K9" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="L9" s="4" t="s">
+      <c r="L9" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="M9" s="4" t="s">
+      <c r="M9" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="N9" s="4" t="s">
+      <c r="N9" s="3" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="41.4">
-      <c r="A10" s="4">
+      <c r="A10" s="3">
         <v>66</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="4">
         <v>0</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="J10" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="K10" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="L10" s="4" t="s">
+      <c r="L10" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="M10" s="4" t="s">
+      <c r="M10" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="N10" s="4" t="s">
+      <c r="N10" s="3" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="27.6">
-      <c r="A11" s="4">
+      <c r="A11" s="3">
         <v>67</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11" s="4">
         <v>0</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="J11" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="K11" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="L11" s="4" t="s">
+      <c r="L11" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="M11" s="4" t="s">
+      <c r="M11" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="N11" s="4" t="s">
+      <c r="N11" s="3" t="s">
         <v>247</v>
       </c>
     </row>
@@ -6766,22 +6766,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="19.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
     </row>
     <row r="2" spans="1:14" ht="14.4">
       <c r="A2" s="6" t="s">
@@ -6802,220 +6802,220 @@
       <c r="N2" s="6"/>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="L4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="M4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="N4" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="27.6">
-      <c r="A5" s="4">
+      <c r="A5" s="3">
         <v>29</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="4">
         <v>0</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="L5" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="M5" s="4" t="s">
+      <c r="M5" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="N5" s="4"/>
+      <c r="N5" s="3"/>
     </row>
     <row r="6" spans="1:14" ht="27.6">
-      <c r="A6" s="4">
+      <c r="A6" s="3">
         <v>30</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="4">
         <v>0</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="L6" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="M6" s="4" t="s">
+      <c r="M6" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="N6" s="4" t="s">
+      <c r="N6" s="3" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="27.6">
-      <c r="A7" s="4">
+      <c r="A7" s="3">
         <v>65</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="4">
         <v>0</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="J7" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="K7" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="L7" s="4" t="s">
+      <c r="L7" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="M7" s="4" t="s">
+      <c r="M7" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="N7" s="4" t="s">
+      <c r="N7" s="3" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="27.6">
-      <c r="A8" s="4">
+      <c r="A8" s="3">
         <v>68</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="4">
         <v>0</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="J8" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="L8" s="4" t="s">
+      <c r="L8" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="M8" s="4" t="s">
+      <c r="M8" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="N8" s="4" t="s">
+      <c r="N8" s="3" t="s">
         <v>316</v>
       </c>
     </row>
@@ -7155,22 +7155,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="19.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
     </row>
     <row r="2" spans="1:14" ht="14.4">
       <c r="A2" s="6" t="s">
@@ -7191,570 +7191,570 @@
       <c r="N2" s="6"/>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="L4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="M4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="N4" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="27.6">
-      <c r="A5" s="4">
+      <c r="A5" s="3">
         <v>48</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="4">
         <v>0</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="L5" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="M5" s="4" t="s">
+      <c r="M5" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="N5" s="4" t="s">
+      <c r="N5" s="3" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="27.6">
-      <c r="A6" s="4">
+      <c r="A6" s="3">
         <v>49</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="4">
         <v>0</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="L6" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="M6" s="4" t="s">
+      <c r="M6" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="N6" s="4" t="s">
+      <c r="N6" s="3" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="27.6">
-      <c r="A7" s="4">
+      <c r="A7" s="3">
         <v>50</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="4">
         <v>0</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="J7" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="K7" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="L7" s="4" t="s">
+      <c r="L7" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="M7" s="4" t="s">
+      <c r="M7" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="N7" s="4" t="s">
+      <c r="N7" s="3" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="27.6">
-      <c r="A8" s="4">
+      <c r="A8" s="3">
         <v>51</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="4">
         <v>0</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="J8" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="L8" s="4" t="s">
+      <c r="L8" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="M8" s="4" t="s">
+      <c r="M8" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="N8" s="4" t="s">
+      <c r="N8" s="3" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="27.6">
-      <c r="A9" s="4">
+      <c r="A9" s="3">
         <v>52</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="4">
         <v>0</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="J9" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="K9" s="4" t="s">
+      <c r="K9" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="L9" s="4" t="s">
+      <c r="L9" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="M9" s="4" t="s">
+      <c r="M9" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="N9" s="4"/>
+      <c r="N9" s="3"/>
     </row>
     <row r="10" spans="1:14" ht="27.6">
-      <c r="A10" s="4">
+      <c r="A10" s="3">
         <v>53</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="4">
         <v>0</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="J10" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="K10" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="L10" s="4" t="s">
+      <c r="L10" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="M10" s="4" t="s">
+      <c r="M10" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="N10" s="4"/>
+      <c r="N10" s="3"/>
     </row>
     <row r="11" spans="1:14" ht="41.4">
-      <c r="A11" s="4">
+      <c r="A11" s="3">
         <v>54</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11" s="4">
         <v>0</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="J11" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="K11" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="L11" s="4" t="s">
+      <c r="L11" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="M11" s="4" t="s">
+      <c r="M11" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="N11" s="4" t="s">
+      <c r="N11" s="3" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="27.6">
-      <c r="A12" s="4">
+      <c r="A12" s="3">
         <v>57</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="4">
         <v>0</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J12" s="4" t="s">
+      <c r="J12" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="K12" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="L12" s="4" t="s">
+      <c r="L12" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="M12" s="4" t="s">
+      <c r="M12" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="N12" s="4" t="s">
+      <c r="N12" s="3" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="27.6">
-      <c r="A13" s="4">
+      <c r="A13" s="3">
         <v>39</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H13" s="4">
         <v>0</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J13" s="4" t="s">
+      <c r="J13" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="K13" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="L13" s="4" t="s">
+      <c r="L13" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="M13" s="4" t="s">
+      <c r="M13" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="N13" s="4" t="s">
+      <c r="N13" s="3" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="27.6">
-      <c r="A14" s="4">
+      <c r="A14" s="3">
         <v>62</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H14" s="5">
+      <c r="H14" s="4">
         <v>0</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="4" t="s">
+      <c r="J14" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="K14" s="4" t="s">
+      <c r="K14" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="L14" s="4" t="s">
+      <c r="L14" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="M14" s="4" t="s">
+      <c r="M14" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="N14" s="4" t="s">
+      <c r="N14" s="3" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="27.6">
-      <c r="A15" s="4">
+      <c r="A15" s="3">
         <v>63</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H15" s="4">
         <v>0</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="I15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J15" s="4" t="s">
+      <c r="J15" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="K15" s="4" t="s">
+      <c r="K15" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="L15" s="4" t="s">
+      <c r="L15" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="M15" s="4" t="s">
+      <c r="M15" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="N15" s="4" t="s">
+      <c r="N15" s="3" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="41.4">
-      <c r="A16" s="4">
+      <c r="A16" s="3">
         <v>64</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H16" s="5">
+      <c r="H16" s="4">
         <v>0</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="I16" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J16" s="4" t="s">
+      <c r="J16" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="K16" s="4" t="s">
+      <c r="K16" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="L16" s="4" t="s">
+      <c r="L16" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="M16" s="4" t="s">
+      <c r="M16" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="N16" s="4" t="s">
+      <c r="N16" s="3" t="s">
         <v>391</v>
       </c>
     </row>
@@ -7894,22 +7894,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="19.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>392</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
     </row>
     <row r="2" spans="1:14" ht="14.4">
       <c r="A2" s="6" t="s">
@@ -7930,352 +7930,352 @@
       <c r="N2" s="6"/>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="L4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="M4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="N4" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="27.6">
-      <c r="A5" s="4">
+      <c r="A5" s="3">
         <v>6</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="4">
         <v>0</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="L5" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="M5" s="4" t="s">
+      <c r="M5" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="N5" s="4" t="s">
+      <c r="N5" s="3" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="41.4">
-      <c r="A6" s="4">
+      <c r="A6" s="3">
         <v>60</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="4">
         <v>0</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="L6" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="M6" s="4" t="s">
+      <c r="M6" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="N6" s="4" t="s">
+      <c r="N6" s="3" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="27.6">
-      <c r="A7" s="4">
+      <c r="A7" s="3">
         <v>70</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="4">
         <v>0</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="J7" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="K7" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="L7" s="4" t="s">
+      <c r="L7" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="M7" s="4" t="s">
+      <c r="M7" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="N7" s="4"/>
+      <c r="N7" s="3"/>
     </row>
     <row r="8" spans="1:14" ht="27.6">
-      <c r="A8" s="4">
+      <c r="A8" s="3">
         <v>71</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="4">
         <v>0</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="J8" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="L8" s="4" t="s">
+      <c r="L8" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="M8" s="4" t="s">
+      <c r="M8" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="N8" s="4" t="s">
+      <c r="N8" s="3" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="27.6">
-      <c r="A9" s="4">
+      <c r="A9" s="3">
         <v>72</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="4">
         <v>0</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="J9" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="K9" s="4" t="s">
+      <c r="K9" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="L9" s="4" t="s">
+      <c r="L9" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="M9" s="4" t="s">
+      <c r="M9" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="N9" s="4" t="s">
+      <c r="N9" s="3" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="27.6">
-      <c r="A10" s="4">
+      <c r="A10" s="3">
         <v>73</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="4">
         <v>0</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="J10" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="K10" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="L10" s="4" t="s">
+      <c r="L10" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="M10" s="4" t="s">
+      <c r="M10" s="3" t="s">
         <v>428</v>
       </c>
-      <c r="N10" s="4" t="s">
+      <c r="N10" s="3" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="27.6">
-      <c r="A11" s="4">
+      <c r="A11" s="3">
         <v>75</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11" s="4">
         <v>0</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="J11" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="K11" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="L11" s="4" t="s">
+      <c r="L11" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="M11" s="4" t="s">
+      <c r="M11" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="N11" s="4" t="s">
+      <c r="N11" s="3" t="s">
         <v>436</v>
       </c>
     </row>
@@ -8415,22 +8415,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="19.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>437</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
     </row>
     <row r="2" spans="1:14" ht="14.4">
       <c r="A2" s="6" t="s">
@@ -8451,618 +8451,618 @@
       <c r="N2" s="6"/>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="L4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="M4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="N4" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="27.6">
-      <c r="A5" s="4">
+      <c r="A5" s="3">
         <v>17</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="4">
         <v>0</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="L5" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="M5" s="4" t="s">
+      <c r="M5" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="N5" s="4" t="s">
+      <c r="N5" s="3" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="27.6">
-      <c r="A6" s="4">
+      <c r="A6" s="3">
         <v>18</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="4">
         <v>0</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="L6" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="M6" s="4" t="s">
+      <c r="M6" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="N6" s="4" t="s">
+      <c r="N6" s="3" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="27.6">
-      <c r="A7" s="4">
+      <c r="A7" s="3">
         <v>41</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="4">
         <v>0</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="J7" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="K7" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="L7" s="4" t="s">
+      <c r="L7" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="M7" s="4" t="s">
+      <c r="M7" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="N7" s="4" t="s">
+      <c r="N7" s="3" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="41.4">
-      <c r="A8" s="4">
+      <c r="A8" s="3">
         <v>42</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="4">
         <v>0</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="J8" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="L8" s="4" t="s">
+      <c r="L8" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="M8" s="4" t="s">
+      <c r="M8" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="N8" s="4" t="s">
+      <c r="N8" s="3" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="27.6">
-      <c r="A9" s="4">
+      <c r="A9" s="3">
         <v>43</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="4">
         <v>0</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="J9" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="K9" s="4" t="s">
+      <c r="K9" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="L9" s="4" t="s">
+      <c r="L9" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="M9" s="4" t="s">
+      <c r="M9" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="N9" s="4" t="s">
+      <c r="N9" s="3" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="27.6">
-      <c r="A10" s="4">
+      <c r="A10" s="3">
         <v>44</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="4">
         <v>0</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="J10" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="K10" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="L10" s="4" t="s">
+      <c r="L10" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="M10" s="4" t="s">
+      <c r="M10" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="N10" s="4" t="s">
+      <c r="N10" s="3" t="s">
         <v>474</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="27.6">
-      <c r="A11" s="4">
+      <c r="A11" s="3">
         <v>45</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11" s="4">
         <v>0</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="J11" s="3" t="s">
         <v>476</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="K11" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="L11" s="4" t="s">
+      <c r="L11" s="3" t="s">
         <v>478</v>
       </c>
-      <c r="M11" s="4" t="s">
+      <c r="M11" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="N11" s="4" t="s">
+      <c r="N11" s="3" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="27.6">
-      <c r="A12" s="4">
+      <c r="A12" s="3">
         <v>46</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="4">
         <v>0</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J12" s="4" t="s">
+      <c r="J12" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="K12" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="L12" s="4" t="s">
+      <c r="L12" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="M12" s="4" t="s">
+      <c r="M12" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="N12" s="4" t="s">
+      <c r="N12" s="3" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="27.6">
-      <c r="A13" s="4">
+      <c r="A13" s="3">
         <v>47</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H13" s="4">
         <v>0</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J13" s="4" t="s">
+      <c r="J13" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="K13" s="3" t="s">
         <v>489</v>
       </c>
-      <c r="L13" s="4" t="s">
+      <c r="L13" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="M13" s="4" t="s">
+      <c r="M13" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="N13" s="4" t="s">
+      <c r="N13" s="3" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="27.6">
-      <c r="A14" s="4">
+      <c r="A14" s="3">
         <v>55</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H14" s="5">
+      <c r="H14" s="4">
         <v>0</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J14" s="4" t="s">
+      <c r="J14" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="K14" s="4" t="s">
+      <c r="K14" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="L14" s="4" t="s">
+      <c r="L14" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="M14" s="4" t="s">
+      <c r="M14" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="N14" s="4" t="s">
+      <c r="N14" s="3" t="s">
         <v>498</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="27.6">
-      <c r="A15" s="4">
+      <c r="A15" s="3">
         <v>56</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H15" s="4">
         <v>0</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="I15" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J15" s="4" t="s">
+      <c r="J15" s="3" t="s">
         <v>500</v>
       </c>
-      <c r="K15" s="4" t="s">
+      <c r="K15" s="3" t="s">
         <v>501</v>
       </c>
-      <c r="L15" s="4" t="s">
+      <c r="L15" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="M15" s="4" t="s">
+      <c r="M15" s="3" t="s">
         <v>503</v>
       </c>
-      <c r="N15" s="4" t="s">
+      <c r="N15" s="3" t="s">
         <v>504</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="27.6">
-      <c r="A16" s="4">
+      <c r="A16" s="3">
         <v>74</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H16" s="5">
+      <c r="H16" s="4">
         <v>0</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="I16" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J16" s="4" t="s">
+      <c r="J16" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="K16" s="4" t="s">
+      <c r="K16" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="L16" s="4" t="s">
+      <c r="L16" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="M16" s="4" t="s">
+      <c r="M16" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="N16" s="4" t="s">
+      <c r="N16" s="3" t="s">
         <v>511</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="27.6">
-      <c r="A17" s="4">
+      <c r="A17" s="3">
         <v>76</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H17" s="5">
+      <c r="H17" s="4">
         <v>0</v>
       </c>
-      <c r="I17" s="4" t="s">
+      <c r="I17" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J17" s="4" t="s">
+      <c r="J17" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="K17" s="4" t="s">
+      <c r="K17" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="L17" s="4" t="s">
+      <c r="L17" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="M17" s="4" t="s">
+      <c r="M17" s="3" t="s">
         <v>516</v>
       </c>
-      <c r="N17" s="4" t="s">
+      <c r="N17" s="3" t="s">
         <v>74</v>
       </c>
     </row>
